--- a/artfynd/A 49085-2023 artfynd.xlsx
+++ b/artfynd/A 49085-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193400</v>
       </c>
       <c r="B2" t="n">
-        <v>89332</v>
+        <v>89334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49085-2023 artfynd.xlsx
+++ b/artfynd/A 49085-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193400</v>
       </c>
       <c r="B2" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136193399</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136193401</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136193402</v>
       </c>
       <c r="B5" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136193408</v>
       </c>
       <c r="B6" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49085-2023 artfynd.xlsx
+++ b/artfynd/A 49085-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193400</v>
       </c>
       <c r="B2" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
